--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119656811</v>
+        <v>119656823</v>
       </c>
       <c r="B24" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699262</v>
+        <v>699254</v>
       </c>
       <c r="R24" t="n">
-        <v>7166090</v>
+        <v>7166128</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119656808</v>
+        <v>119656828</v>
       </c>
       <c r="B25" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699274</v>
+        <v>699327</v>
       </c>
       <c r="R25" t="n">
-        <v>7166183</v>
+        <v>7165987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119656823</v>
+        <v>119656801</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699254</v>
+        <v>699276</v>
       </c>
       <c r="R26" t="n">
-        <v>7166128</v>
+        <v>7166183</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119656828</v>
+        <v>119656811</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699327</v>
+        <v>699262</v>
       </c>
       <c r="R27" t="n">
-        <v>7165987</v>
+        <v>7166090</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119656801</v>
+        <v>119656808</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699276</v>
+        <v>699274</v>
       </c>
       <c r="R28" t="n">
         <v>7166183</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119656831</v>
+        <v>119656814</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699358</v>
+        <v>699416</v>
       </c>
       <c r="R2" t="n">
-        <v>7166256</v>
+        <v>7166294</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119656825</v>
+        <v>119656799</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699263</v>
+        <v>699365</v>
       </c>
       <c r="R3" t="n">
-        <v>7166031</v>
+        <v>7166235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119656799</v>
+        <v>119656804</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699365</v>
+        <v>699262</v>
       </c>
       <c r="R4" t="n">
-        <v>7166235</v>
+        <v>7166043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119656819</v>
+        <v>119656825</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699281</v>
+        <v>699263</v>
       </c>
       <c r="R5" t="n">
-        <v>7166288</v>
+        <v>7166031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119656802</v>
+        <v>119656805</v>
       </c>
       <c r="B6" t="n">
         <v>91832</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699258</v>
+        <v>699303</v>
       </c>
       <c r="R6" t="n">
-        <v>7166094</v>
+        <v>7166109</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119656820</v>
+        <v>119656826</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699282</v>
+        <v>699275</v>
       </c>
       <c r="R8" t="n">
-        <v>7166276</v>
+        <v>7166007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119656803</v>
+        <v>119656818</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699259</v>
+        <v>699282</v>
       </c>
       <c r="R9" t="n">
-        <v>7166061</v>
+        <v>7166314</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119656821</v>
+        <v>119656806</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699278</v>
+        <v>699383</v>
       </c>
       <c r="R10" t="n">
-        <v>7166255</v>
+        <v>7166485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119656807</v>
+        <v>119656798</v>
       </c>
       <c r="B11" t="n">
-        <v>91863</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699283</v>
+        <v>699309</v>
       </c>
       <c r="R11" t="n">
-        <v>7166289</v>
+        <v>7166504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119656834</v>
+        <v>119656802</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699259</v>
+        <v>699258</v>
       </c>
       <c r="R12" t="n">
-        <v>7166146</v>
+        <v>7166094</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119656818</v>
+        <v>119656820</v>
       </c>
       <c r="B13" t="n">
         <v>91840</v>
@@ -1840,7 +1840,7 @@
         <v>699282</v>
       </c>
       <c r="R13" t="n">
-        <v>7166314</v>
+        <v>7166276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119656796</v>
+        <v>119656811</v>
       </c>
       <c r="B14" t="n">
-        <v>79643</v>
+        <v>91863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699318</v>
+        <v>699262</v>
       </c>
       <c r="R14" t="n">
-        <v>7166136</v>
+        <v>7166090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119656829</v>
+        <v>119656824</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699337</v>
+        <v>699253</v>
       </c>
       <c r="R15" t="n">
-        <v>7166148</v>
+        <v>7166107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119656832</v>
+        <v>119656803</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699398</v>
+        <v>699259</v>
       </c>
       <c r="R16" t="n">
-        <v>7166316</v>
+        <v>7166061</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119656812</v>
+        <v>119656801</v>
       </c>
       <c r="B17" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699269</v>
+        <v>699276</v>
       </c>
       <c r="R17" t="n">
-        <v>7166050</v>
+        <v>7166183</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119656827</v>
+        <v>119656816</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699302</v>
+        <v>699282</v>
       </c>
       <c r="R18" t="n">
-        <v>7166006</v>
+        <v>7166368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119656805</v>
+        <v>119656829</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699303</v>
+        <v>699337</v>
       </c>
       <c r="R19" t="n">
-        <v>7166109</v>
+        <v>7166148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119656798</v>
+        <v>119656821</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699309</v>
+        <v>699278</v>
       </c>
       <c r="R20" t="n">
-        <v>7166504</v>
+        <v>7166255</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119656810</v>
+        <v>119656819</v>
       </c>
       <c r="B21" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699257</v>
+        <v>699281</v>
       </c>
       <c r="R21" t="n">
-        <v>7166142</v>
+        <v>7166288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119656814</v>
+        <v>119656796</v>
       </c>
       <c r="B22" t="n">
-        <v>91863</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699416</v>
+        <v>699318</v>
       </c>
       <c r="R22" t="n">
-        <v>7166294</v>
+        <v>7166136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119656806</v>
+        <v>119656827</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699383</v>
+        <v>699302</v>
       </c>
       <c r="R23" t="n">
-        <v>7166485</v>
+        <v>7166006</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119656823</v>
+        <v>119656808</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699254</v>
+        <v>699274</v>
       </c>
       <c r="R24" t="n">
-        <v>7166128</v>
+        <v>7166183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119656828</v>
+        <v>119656800</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699327</v>
+        <v>699280</v>
       </c>
       <c r="R25" t="n">
-        <v>7165987</v>
+        <v>7166311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119656801</v>
+        <v>119656834</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699276</v>
+        <v>699259</v>
       </c>
       <c r="R26" t="n">
-        <v>7166183</v>
+        <v>7166146</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119656811</v>
+        <v>119656822</v>
       </c>
       <c r="B27" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699262</v>
+        <v>699258</v>
       </c>
       <c r="R27" t="n">
-        <v>7166090</v>
+        <v>7166143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119656808</v>
+        <v>119656835</v>
       </c>
       <c r="B28" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699274</v>
+        <v>699265</v>
       </c>
       <c r="R28" t="n">
-        <v>7166183</v>
+        <v>7166060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119656826</v>
+        <v>119656807</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699275</v>
+        <v>699283</v>
       </c>
       <c r="R29" t="n">
-        <v>7166007</v>
+        <v>7166289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119656800</v>
+        <v>119656812</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699280</v>
+        <v>699269</v>
       </c>
       <c r="R30" t="n">
-        <v>7166311</v>
+        <v>7166050</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119656804</v>
+        <v>119656836</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699262</v>
+        <v>699409</v>
       </c>
       <c r="R31" t="n">
-        <v>7166043</v>
+        <v>7166313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119656836</v>
+        <v>119656830</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699409</v>
+        <v>699348</v>
       </c>
       <c r="R32" t="n">
-        <v>7166313</v>
+        <v>7166225</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119656835</v>
+        <v>119656823</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699265</v>
+        <v>699254</v>
       </c>
       <c r="R33" t="n">
-        <v>7166060</v>
+        <v>7166128</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119656822</v>
+        <v>119656831</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699258</v>
+        <v>699358</v>
       </c>
       <c r="R34" t="n">
-        <v>7166143</v>
+        <v>7166256</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119656816</v>
+        <v>119656828</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699282</v>
+        <v>699327</v>
       </c>
       <c r="R35" t="n">
-        <v>7166368</v>
+        <v>7165987</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119656830</v>
+        <v>119656832</v>
       </c>
       <c r="B36" t="n">
         <v>91840</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699348</v>
+        <v>699398</v>
       </c>
       <c r="R36" t="n">
-        <v>7166225</v>
+        <v>7166316</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119656824</v>
+        <v>119656810</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699253</v>
+        <v>699257</v>
       </c>
       <c r="R37" t="n">
-        <v>7166107</v>
+        <v>7166142</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119656814</v>
+        <v>119656796</v>
       </c>
       <c r="B2" t="n">
-        <v>91863</v>
+        <v>79643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699416</v>
+        <v>699318</v>
       </c>
       <c r="R2" t="n">
-        <v>7166294</v>
+        <v>7166136</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119656799</v>
+        <v>119656829</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699365</v>
+        <v>699337</v>
       </c>
       <c r="R3" t="n">
-        <v>7166235</v>
+        <v>7166148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119656804</v>
+        <v>119656810</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699262</v>
+        <v>699257</v>
       </c>
       <c r="R4" t="n">
-        <v>7166043</v>
+        <v>7166142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119656825</v>
+        <v>119656828</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699263</v>
+        <v>699327</v>
       </c>
       <c r="R5" t="n">
-        <v>7166031</v>
+        <v>7165987</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119656805</v>
+        <v>119656803</v>
       </c>
       <c r="B6" t="n">
         <v>91832</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699303</v>
+        <v>699259</v>
       </c>
       <c r="R6" t="n">
-        <v>7166109</v>
+        <v>7166061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119656813</v>
+        <v>119656831</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699374</v>
+        <v>699358</v>
       </c>
       <c r="R7" t="n">
-        <v>7166221</v>
+        <v>7166256</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119656826</v>
+        <v>119656798</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699275</v>
+        <v>699309</v>
       </c>
       <c r="R8" t="n">
-        <v>7166007</v>
+        <v>7166504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119656806</v>
+        <v>119656800</v>
       </c>
       <c r="B10" t="n">
         <v>91832</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699383</v>
+        <v>699280</v>
       </c>
       <c r="R10" t="n">
-        <v>7166485</v>
+        <v>7166311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119656798</v>
+        <v>119656825</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699309</v>
+        <v>699263</v>
       </c>
       <c r="R11" t="n">
-        <v>7166504</v>
+        <v>7166031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119656802</v>
+        <v>119656834</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699258</v>
+        <v>699259</v>
       </c>
       <c r="R12" t="n">
-        <v>7166094</v>
+        <v>7166146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119656820</v>
+        <v>119656801</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699282</v>
+        <v>699276</v>
       </c>
       <c r="R13" t="n">
-        <v>7166276</v>
+        <v>7166183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119656811</v>
+        <v>119656822</v>
       </c>
       <c r="B14" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699262</v>
+        <v>699258</v>
       </c>
       <c r="R14" t="n">
-        <v>7166090</v>
+        <v>7166143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119656824</v>
+        <v>119656826</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699253</v>
+        <v>699275</v>
       </c>
       <c r="R15" t="n">
-        <v>7166107</v>
+        <v>7166007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119656803</v>
+        <v>119656799</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699259</v>
+        <v>699365</v>
       </c>
       <c r="R16" t="n">
-        <v>7166061</v>
+        <v>7166235</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119656801</v>
+        <v>119656820</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699276</v>
+        <v>699282</v>
       </c>
       <c r="R17" t="n">
-        <v>7166183</v>
+        <v>7166276</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119656816</v>
+        <v>119656811</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699282</v>
+        <v>699262</v>
       </c>
       <c r="R18" t="n">
-        <v>7166368</v>
+        <v>7166090</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119656829</v>
+        <v>119656814</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699337</v>
+        <v>699416</v>
       </c>
       <c r="R19" t="n">
-        <v>7166148</v>
+        <v>7166294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119656821</v>
+        <v>119656802</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699278</v>
+        <v>699258</v>
       </c>
       <c r="R20" t="n">
-        <v>7166255</v>
+        <v>7166094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119656819</v>
+        <v>119656835</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699281</v>
+        <v>699265</v>
       </c>
       <c r="R21" t="n">
-        <v>7166288</v>
+        <v>7166060</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119656796</v>
+        <v>119656806</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699318</v>
+        <v>699383</v>
       </c>
       <c r="R22" t="n">
-        <v>7166136</v>
+        <v>7166485</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119656808</v>
+        <v>119656821</v>
       </c>
       <c r="B24" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699274</v>
+        <v>699278</v>
       </c>
       <c r="R24" t="n">
-        <v>7166183</v>
+        <v>7166255</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119656800</v>
+        <v>119656832</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699280</v>
+        <v>699398</v>
       </c>
       <c r="R25" t="n">
-        <v>7166311</v>
+        <v>7166316</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119656834</v>
+        <v>119656836</v>
       </c>
       <c r="B26" t="n">
         <v>91834</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699259</v>
+        <v>699409</v>
       </c>
       <c r="R26" t="n">
-        <v>7166146</v>
+        <v>7166313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119656822</v>
+        <v>119656805</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699258</v>
+        <v>699303</v>
       </c>
       <c r="R27" t="n">
-        <v>7166143</v>
+        <v>7166109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119656835</v>
+        <v>119656812</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699265</v>
+        <v>699269</v>
       </c>
       <c r="R28" t="n">
-        <v>7166060</v>
+        <v>7166050</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119656807</v>
+        <v>119656823</v>
       </c>
       <c r="B29" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699283</v>
+        <v>699254</v>
       </c>
       <c r="R29" t="n">
-        <v>7166289</v>
+        <v>7166128</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119656812</v>
+        <v>119656804</v>
       </c>
       <c r="B30" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699269</v>
+        <v>699262</v>
       </c>
       <c r="R30" t="n">
-        <v>7166050</v>
+        <v>7166043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119656836</v>
+        <v>119656819</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3645,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699409</v>
+        <v>699281</v>
       </c>
       <c r="R31" t="n">
-        <v>7166313</v>
+        <v>7166288</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119656830</v>
+        <v>119656813</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3747,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699348</v>
+        <v>699374</v>
       </c>
       <c r="R32" t="n">
-        <v>7166225</v>
+        <v>7166221</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119656823</v>
+        <v>119656824</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699254</v>
+        <v>699253</v>
       </c>
       <c r="R33" t="n">
-        <v>7166128</v>
+        <v>7166107</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119656831</v>
+        <v>119656816</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699358</v>
+        <v>699282</v>
       </c>
       <c r="R34" t="n">
-        <v>7166256</v>
+        <v>7166368</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119656828</v>
+        <v>119656807</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699327</v>
+        <v>699283</v>
       </c>
       <c r="R35" t="n">
-        <v>7165987</v>
+        <v>7166289</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119656832</v>
+        <v>119656808</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4155,25 +4155,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699398</v>
+        <v>699274</v>
       </c>
       <c r="R36" t="n">
-        <v>7166316</v>
+        <v>7166183</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119656810</v>
+        <v>119656830</v>
       </c>
       <c r="B37" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699257</v>
+        <v>699348</v>
       </c>
       <c r="R37" t="n">
-        <v>7166142</v>
+        <v>7166225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119656796</v>
+        <v>119656826</v>
       </c>
       <c r="B2" t="n">
-        <v>79643</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699318</v>
+        <v>699275</v>
       </c>
       <c r="R2" t="n">
-        <v>7166136</v>
+        <v>7166007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119656829</v>
+        <v>119656836</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699337</v>
+        <v>699409</v>
       </c>
       <c r="R3" t="n">
-        <v>7166148</v>
+        <v>7166313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119656810</v>
+        <v>119656825</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699257</v>
+        <v>699263</v>
       </c>
       <c r="R4" t="n">
-        <v>7166142</v>
+        <v>7166031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119656828</v>
+        <v>119656831</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699327</v>
+        <v>699358</v>
       </c>
       <c r="R5" t="n">
-        <v>7165987</v>
+        <v>7166256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119656803</v>
+        <v>119656799</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699259</v>
+        <v>699365</v>
       </c>
       <c r="R6" t="n">
-        <v>7166061</v>
+        <v>7166235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119656831</v>
+        <v>119656820</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699358</v>
+        <v>699282</v>
       </c>
       <c r="R7" t="n">
-        <v>7166256</v>
+        <v>7166276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119656798</v>
+        <v>119656835</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699309</v>
+        <v>699265</v>
       </c>
       <c r="R8" t="n">
-        <v>7166504</v>
+        <v>7166060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119656818</v>
+        <v>119656829</v>
       </c>
       <c r="B9" t="n">
         <v>91840</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699282</v>
+        <v>699337</v>
       </c>
       <c r="R9" t="n">
-        <v>7166314</v>
+        <v>7166148</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119656800</v>
+        <v>119656801</v>
       </c>
       <c r="B10" t="n">
         <v>91832</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699280</v>
+        <v>699276</v>
       </c>
       <c r="R10" t="n">
-        <v>7166311</v>
+        <v>7166183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119656825</v>
+        <v>119656798</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699263</v>
+        <v>699309</v>
       </c>
       <c r="R11" t="n">
-        <v>7166031</v>
+        <v>7166504</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119656834</v>
+        <v>119656828</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699259</v>
+        <v>699327</v>
       </c>
       <c r="R12" t="n">
-        <v>7166146</v>
+        <v>7165987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119656801</v>
+        <v>119656800</v>
       </c>
       <c r="B13" t="n">
         <v>91832</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699276</v>
+        <v>699280</v>
       </c>
       <c r="R13" t="n">
-        <v>7166183</v>
+        <v>7166311</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119656822</v>
+        <v>119656824</v>
       </c>
       <c r="B14" t="n">
         <v>91840</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699258</v>
+        <v>699253</v>
       </c>
       <c r="R14" t="n">
-        <v>7166143</v>
+        <v>7166107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119656826</v>
+        <v>119656821</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699275</v>
+        <v>699278</v>
       </c>
       <c r="R15" t="n">
-        <v>7166007</v>
+        <v>7166255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119656799</v>
+        <v>119656802</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699365</v>
+        <v>699258</v>
       </c>
       <c r="R16" t="n">
-        <v>7166235</v>
+        <v>7166094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119656820</v>
+        <v>119656834</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699282</v>
+        <v>699259</v>
       </c>
       <c r="R17" t="n">
-        <v>7166276</v>
+        <v>7166146</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119656811</v>
+        <v>119656823</v>
       </c>
       <c r="B18" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699262</v>
+        <v>699254</v>
       </c>
       <c r="R18" t="n">
-        <v>7166090</v>
+        <v>7166128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119656814</v>
+        <v>119656808</v>
       </c>
       <c r="B19" t="n">
         <v>91863</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699416</v>
+        <v>699274</v>
       </c>
       <c r="R19" t="n">
-        <v>7166294</v>
+        <v>7166183</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119656802</v>
+        <v>119656810</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699258</v>
+        <v>699257</v>
       </c>
       <c r="R20" t="n">
-        <v>7166094</v>
+        <v>7166142</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119656835</v>
+        <v>119656822</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699265</v>
+        <v>699258</v>
       </c>
       <c r="R21" t="n">
-        <v>7166060</v>
+        <v>7166143</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119656806</v>
+        <v>119656796</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699383</v>
+        <v>699318</v>
       </c>
       <c r="R22" t="n">
-        <v>7166485</v>
+        <v>7166136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119656827</v>
+        <v>119656830</v>
       </c>
       <c r="B23" t="n">
         <v>91840</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699302</v>
+        <v>699348</v>
       </c>
       <c r="R23" t="n">
-        <v>7166006</v>
+        <v>7166225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119656821</v>
+        <v>119656827</v>
       </c>
       <c r="B24" t="n">
         <v>91840</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699278</v>
+        <v>699302</v>
       </c>
       <c r="R24" t="n">
-        <v>7166255</v>
+        <v>7166006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119656832</v>
+        <v>119656805</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699398</v>
+        <v>699303</v>
       </c>
       <c r="R25" t="n">
-        <v>7166316</v>
+        <v>7166109</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119656836</v>
+        <v>119656807</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699409</v>
+        <v>699283</v>
       </c>
       <c r="R26" t="n">
-        <v>7166313</v>
+        <v>7166289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119656805</v>
+        <v>119656832</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699303</v>
+        <v>699398</v>
       </c>
       <c r="R27" t="n">
-        <v>7166109</v>
+        <v>7166316</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119656812</v>
+        <v>119656804</v>
       </c>
       <c r="B28" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699269</v>
+        <v>699262</v>
       </c>
       <c r="R28" t="n">
-        <v>7166050</v>
+        <v>7166043</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119656823</v>
+        <v>119656806</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699254</v>
+        <v>699383</v>
       </c>
       <c r="R29" t="n">
-        <v>7166128</v>
+        <v>7166485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119656804</v>
+        <v>119656803</v>
       </c>
       <c r="B30" t="n">
         <v>91832</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699262</v>
+        <v>699259</v>
       </c>
       <c r="R30" t="n">
-        <v>7166043</v>
+        <v>7166061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119656813</v>
+        <v>119656812</v>
       </c>
       <c r="B32" t="n">
         <v>91863</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699374</v>
+        <v>699269</v>
       </c>
       <c r="R32" t="n">
-        <v>7166221</v>
+        <v>7166050</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119656824</v>
+        <v>119656813</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699253</v>
+        <v>699374</v>
       </c>
       <c r="R33" t="n">
-        <v>7166107</v>
+        <v>7166221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119656816</v>
+        <v>119656818</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -3982,7 +3982,7 @@
         <v>699282</v>
       </c>
       <c r="R34" t="n">
-        <v>7166368</v>
+        <v>7166314</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119656807</v>
+        <v>119656814</v>
       </c>
       <c r="B35" t="n">
         <v>91863</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699283</v>
+        <v>699416</v>
       </c>
       <c r="R35" t="n">
-        <v>7166289</v>
+        <v>7166294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119656808</v>
+        <v>119656811</v>
       </c>
       <c r="B36" t="n">
         <v>91863</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699274</v>
+        <v>699262</v>
       </c>
       <c r="R36" t="n">
-        <v>7166183</v>
+        <v>7166090</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119656830</v>
+        <v>119656816</v>
       </c>
       <c r="B37" t="n">
         <v>91840</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699348</v>
+        <v>699282</v>
       </c>
       <c r="R37" t="n">
-        <v>7166225</v>
+        <v>7166368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119656814</v>
+        <v>119656816</v>
       </c>
       <c r="B35" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699416</v>
+        <v>699282</v>
       </c>
       <c r="R35" t="n">
-        <v>7166294</v>
+        <v>7166368</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119656811</v>
+        <v>119656814</v>
       </c>
       <c r="B36" t="n">
         <v>91863</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699262</v>
+        <v>699416</v>
       </c>
       <c r="R36" t="n">
-        <v>7166090</v>
+        <v>7166294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119656816</v>
+        <v>119656811</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699282</v>
+        <v>699262</v>
       </c>
       <c r="R37" t="n">
-        <v>7166368</v>
+        <v>7166090</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119656816</v>
+        <v>119656814</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4053,25 +4053,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699282</v>
+        <v>699416</v>
       </c>
       <c r="R35" t="n">
-        <v>7166368</v>
+        <v>7166294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119656814</v>
+        <v>119656811</v>
       </c>
       <c r="B36" t="n">
         <v>91863</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699416</v>
+        <v>699262</v>
       </c>
       <c r="R36" t="n">
-        <v>7166294</v>
+        <v>7166090</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119656811</v>
+        <v>119656816</v>
       </c>
       <c r="B37" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4257,25 +4257,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699262</v>
+        <v>699282</v>
       </c>
       <c r="R37" t="n">
-        <v>7166090</v>
+        <v>7166368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 15152-2024 artfynd.xlsx
+++ b/artfynd/A 15152-2024 artfynd.xlsx
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119656808</v>
+        <v>119656810</v>
       </c>
       <c r="B19" t="n">
         <v>91863</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699274</v>
+        <v>699257</v>
       </c>
       <c r="R19" t="n">
-        <v>7166183</v>
+        <v>7166142</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119656810</v>
+        <v>119656808</v>
       </c>
       <c r="B20" t="n">
         <v>91863</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699257</v>
+        <v>699274</v>
       </c>
       <c r="R20" t="n">
-        <v>7166142</v>
+        <v>7166183</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
